--- a/output/hotels_Bangkok_2026-06-01.xlsx
+++ b/output/hotels_Bangkok_2026-06-01.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bangkok Hotels" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hotels" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +26,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -56,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,47 +56,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B0C4DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B0C4DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B0C4DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B0C4DE"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,460 +431,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Hotel Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Price/Night (USD)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total Price (3 nights)</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Total Price (3n)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Capella Bangkok</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="C2" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="2" t="n">
         <v>441</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mandarin Oriental Bangkok</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>135</v>
+      </c>
+      <c r="D3" t="n">
+        <v>405</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Siam Kempinski Hotel Bangkok</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="C4" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D4" s="2" t="n">
         <v>447</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E4" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Siam</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Peninsula Bangkok</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>142</v>
+      </c>
+      <c r="D5" t="n">
+        <v>426</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Shangri-La Bangkok</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="C6" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D6" s="2" t="n">
         <v>444</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Four Seasons Bangkok</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>144</v>
+      </c>
+      <c r="D7" t="n">
+        <v>432</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Chao Phraya</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Anantara Riverside Bangkok Resort</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="C8" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D8" s="2" t="n">
         <v>429</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="E8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Arun Residence</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="C9" t="n">
         <v>55</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D9" t="n">
         <v>165</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E9" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Old City</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Centara Grand at CentralWorld</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="C10" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="D10" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="E10" s="2" t="n">
         <v>8.9</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Siam</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VIE Hotel Bangkok MGallery</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>125</v>
+      </c>
+      <c r="D11" t="n">
+        <v>375</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Siam</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SO/ Bangkok</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Silom</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>The Westin Grande Sukhumvit</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="C13" t="n">
         <v>145</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D13" t="n">
         <v>435</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Sukhumvit</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Sala Rattanakosin Hotel</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="C14" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="D14" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="E14" s="2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Old City</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sindhorn Midtown Hotel Bangkok</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>120</v>
+      </c>
+      <c r="D15" t="n">
+        <v>360</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Langsuan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Pullman Bangkok Hotel G</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="C16" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D16" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E16" s="2" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Silom</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Riva Surya Bangkok</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="C17" t="n">
         <v>99</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="D17" t="n">
         <v>297</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="E17" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>The Sukhumvit Hotel Bangkok</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="C18" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D18" s="2" t="n">
         <v>294</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>8.6</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Sukhumvit</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Amari Bangkok</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="C19" t="n">
         <v>118</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="D19" t="n">
         <v>354</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="E19" t="n">
         <v>8.6</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Siam</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Novotel Bangkok on Siam Square</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="C20" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D20" s="2" t="n">
         <v>324</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E20" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Siam</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Novotel Bangkok Sukhumvit 20</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="C21" t="n">
         <v>112</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="D21" t="n">
         <v>336</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="E21" t="n">
         <v>8.4</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Sukhumvit</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Citadines Sukhumvit 8 Bangkok</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Sukhumvit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Holiday Inn Bangkok Silom</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>285</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Silom</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ibis Bangkok Sukhumvit 24</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Sukhumvit</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Mercure Bangkok Siam</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>246</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Siam</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Narai Hotel Bangkok</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Silom</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Tawana Bangkok Hotel</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>195</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Silom</t>
         </is>
       </c>
     </row>
